--- a/Python_configuration_table_code/Injection_Table/InjectionTable.xlsx
+++ b/Python_configuration_table_code/Injection_Table/InjectionTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>NAME</t>
   </si>
@@ -47,10 +47,13 @@
     <t>Server</t>
   </si>
   <si>
+    <t>D:\NewWorkProject\Vscode\GodotProject\GodotPythonProject\Godot_Configuration_Table_Injection\00_Engine\InjectionTable_Engine\MultiplayerOnline\Server\server.tscn</t>
+  </si>
+  <si>
     <t>Login</t>
   </si>
   <si>
-    <t>D:\NewWorkProject\Vscode\GodotProject\GodotPythonProject\Godot_Configuration_Table_Injection\00_Engine\InjectionTable_Engine\LoginSystem.tscn</t>
+    <t>D:\NewWorkProject\Vscode\GodotProject\GodotPythonProject\Godot_Configuration_Table_Injection\00_Engine\InjectionTable_Engine\LoginSystem\login_system.tscn</t>
   </si>
   <si>
     <t>D:\NewWorkProject\Vscode\GodotProject\GodotPythonProject\Godot_Configuration_Table_Injection\00_Engine\InjectionTable_Engine\LoginSystem\Global_Script.gd</t>
@@ -1008,9 +1011,11 @@
       <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2"/>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
       <c r="C2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" t="b">
         <v>0</v>
@@ -1018,10 +1023,10 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" t="b">
         <v>1</v>
@@ -1030,7 +1035,7 @@
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/Python_configuration_table_code/Injection_Table/InjectionTable.xlsx
+++ b/Python_configuration_table_code/Injection_Table/InjectionTable.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>NAME</t>
   </si>
@@ -57,6 +57,12 @@
   </si>
   <si>
     <t>D:\NewWorkProject\Vscode\GodotProject\GodotPythonProject\Godot_Configuration_Table_Injection\00_Engine\InjectionTable_Engine\LoginSystem\Global_Script.gd</t>
+  </si>
+  <si>
+    <t>AiModel</t>
+  </si>
+  <si>
+    <t>D:\NewWorkProject\Vscode\GodotProject\GodotPythonProject\Godot_Configuration_Table_Injection\00_Engine\InjectionTable_Engine\AiModel\ai_model.tscn</t>
   </si>
 </sst>
 </file>
@@ -987,8 +993,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="4"/>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="4"/>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
@@ -1036,6 +1042,20 @@
       </c>
       <c r="E3" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D4" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
